--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C691"/>
+  <dimension ref="A1:C700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Record DOI HTTPS link is failling: https://doi.org/10.21966/1.715699 status_code=502</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
+          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Record DOI HTTPS link is failling: https://doi.org/10.21966/exy6-1k58 status_code=502</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7604,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>Record DOI HTTPS link is failling: https://doi.org/10.21966/f9m6-qg12 status_code=502</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7634,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7739,12 +7739,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7754,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7949,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8114,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8309,12 +8309,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8849,12 +8849,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -9104,12 +9104,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9134,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9164,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -9254,12 +9254,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -9299,12 +9299,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9464,12 +9464,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -9479,12 +9479,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Pontier, Ondine</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9584,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -9614,12 +9614,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9704,12 +9704,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -9839,12 +9839,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9854,12 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9884,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9929,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -10004,12 +10004,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -10109,12 +10109,12 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10184,12 +10184,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10334,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10364,12 +10364,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10379,12 +10379,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10409,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -10439,12 +10439,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10454,12 +10454,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10499,12 +10499,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10544,12 +10544,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -10619,12 +10619,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10634,12 +10634,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10664,12 +10664,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10739,12 +10739,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10769,12 +10769,147 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Viner, Nick</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>690</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Holmes, Keith</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>691</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Hare, Alex</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>692</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Floyd, William C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>693</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>694</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Whalen, Matt</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>695</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
           <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr">
+      <c r="C697" t="inlineStr">
         <is>
           <t>Contact missing ORCID: Hare, Alex</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>696</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>697</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>698</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Record DOI HTTPS link is failling: https://doi.org/10.21966/1.715699 status_code=502</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Record DOI HTTPS link is failling: https://doi.org/10.21966/exy6-1k58 status_code=502</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Record DOI HTTPS link is failling: https://doi.org/10.21966/f9m6-qg12 status_code=502</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7739,12 +7739,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7949,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8309,12 +8309,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9134,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9164,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9254,12 +9254,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9284,12 +9284,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Pontier, Ondine</t>
         </is>
       </c>
     </row>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9584,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9614,12 +9614,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9929,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -10004,12 +10004,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10109,12 +10109,12 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -10739,12 +10739,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10769,12 +10769,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10784,12 +10784,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10799,12 +10799,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -10814,12 +10814,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
+          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8309,12 +8309,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8849,12 +8849,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10739,12 +10739,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10769,12 +10769,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -10784,12 +10784,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10799,12 +10799,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10814,12 +10814,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10859,12 +10859,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10904,12 +10904,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
+          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -9434,12 +9434,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9464,12 +9464,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10799,12 +10799,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10814,12 +10814,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10859,12 +10859,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -10904,12 +10904,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C700"/>
+  <dimension ref="A1:C686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ondine Pontier' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Daniel Okamoto' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Mathew Brown' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Natalie Mahara' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7604,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7634,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7739,12 +7739,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7754,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7829,12 +7829,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7844,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8114,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8849,12 +8849,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -9104,12 +9104,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9134,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -9284,12 +9284,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9299,12 +9299,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Pontier, Ondine</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -9434,12 +9434,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9449,12 +9449,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -9464,12 +9464,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9479,12 +9479,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9584,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9614,12 +9614,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -9704,12 +9704,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -9839,12 +9839,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9854,12 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9884,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -9944,12 +9944,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -10004,12 +10004,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10109,12 +10109,12 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -10184,12 +10184,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10334,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10409,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10439,12 +10439,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10454,12 +10454,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10499,12 +10499,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -10544,12 +10544,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10589,12 +10589,12 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10604,12 +10604,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10619,12 +10619,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -10634,12 +10634,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Whalen, Matt</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10664,12 +10664,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -10694,220 +10694,10 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
-        </is>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="n">
-        <v>685</v>
-      </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
-        </is>
-      </c>
-      <c r="C687" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
-        </is>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="n">
-        <v>686</v>
-      </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C688" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="n">
-        <v>687</v>
-      </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="n">
-        <v>688</v>
-      </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="n">
-        <v>689</v>
-      </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
-        </is>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="n">
-        <v>690</v>
-      </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
-        </is>
-      </c>
-      <c r="C692" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="n">
-        <v>691</v>
-      </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
-        </is>
-      </c>
-      <c r="C693" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="n">
-        <v>692</v>
-      </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
-        </is>
-      </c>
-      <c r="C694" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="n">
-        <v>693</v>
-      </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
-        </is>
-      </c>
-      <c r="C695" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="n">
-        <v>694</v>
-      </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
-        </is>
-      </c>
-      <c r="C696" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="n">
-        <v>695</v>
-      </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="n">
-        <v>696</v>
-      </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C698" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="n">
-        <v>697</v>
-      </c>
-      <c r="B699" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C699" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
-        </is>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="n">
-        <v>698</v>
-      </c>
-      <c r="B700" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C700" t="inlineStr">
         <is>
           <t>Contact missing ORCID: Floyd, William C.</t>
         </is>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C686"/>
+  <dimension ref="A1:C674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Daniel Okamoto' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. Okamoto' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Thea Mai' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/0z9k-cc28' (IsIdenticalTo) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4439,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7604,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7634,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7739,12 +7739,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7754,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7829,12 +7829,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7844,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7949,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8114,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8309,12 +8309,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
+          <t>Invalid Resource URL: http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf returned status_code=timeout</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -8849,12 +8849,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -9104,12 +9104,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9134,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9164,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9284,12 +9284,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -9299,12 +9299,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Pontier, Ondine</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>7a9adcca-b0dc-462f-aa3f-9bb9209158be</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -9434,12 +9434,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -9449,12 +9449,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -9464,12 +9464,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -9479,12 +9479,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9584,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9614,12 +9614,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9704,12 +9704,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -9839,12 +9839,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9854,12 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9884,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9929,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -10004,12 +10004,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -10109,12 +10109,12 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10184,12 +10184,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10334,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -10364,12 +10364,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10379,12 +10379,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10409,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10439,12 +10439,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -10454,12 +10454,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Whalen, Matt</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -10499,12 +10499,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10514,192 +10514,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="n">
-        <v>673</v>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="n">
-        <v>674</v>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="n">
-        <v>675</v>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="n">
-        <v>676</v>
-      </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="n">
-        <v>677</v>
-      </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
-        <is>
           <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="n">
-        <v>678</v>
-      </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="n">
-        <v>679</v>
-      </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="n">
-        <v>680</v>
-      </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
-        </is>
-      </c>
-      <c r="C682" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="n">
-        <v>681</v>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
-        </is>
-      </c>
-      <c r="C683" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="n">
-        <v>682</v>
-      </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="n">
-        <v>683</v>
-      </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="n">
-        <v>684</v>
-      </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C686" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7739,12 +7739,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7754,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -9104,12 +9104,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -9254,12 +9254,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -10439,12 +10439,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Whalen, Matt</t>
         </is>
       </c>
     </row>
@@ -10454,12 +10454,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C674"/>
+  <dimension ref="A1:C666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Maartje Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>550e7acb-0e3f-461f-bd47-8b6ced16bf43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>773ef9a6-64dd-4734-ba16-566470b0edad</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2b33a5f0-1172-41e4-8330-b4c77d1665c7</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>8a7cd5ea-e167-419e-a5c3-919acafe8455</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_seagrassdensitysurveys' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d1ae4278b4' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4439,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/pacrim47961.2019.8985053' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Angeleen Olson' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D Haggarty' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Francis Juanes' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'H Hakai Geospatial' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6044,12 +6044,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>9001166d-e7eb-410f-92d6-17df0593cb2e</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/m5rv-4f16' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carolyn Prentice' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katrina Poppe' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1029/2019gb006345' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/0xex-r023' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.48321/D18S8D' (Documents) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>eb02906a-9645-4486-ba14-46d71c581352</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>d3c4dde5-38b2-480d-a4e7-228bde9eb537</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Institute Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/xp9x-m243' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6704,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Team' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Isabelle Desmarais' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Robert White' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.1.0' | DataCite='2.0'</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Tyrel Froese' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Gillian Sadlier-Brown' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1109/igarss.2012.6351194' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.3389/fmars.2022.968470' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0247208</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at Sitka Harbor, Sitka, Alaska, USA (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content, water temperature, sea surface salinity and other parameters collected in Sitka Harbor, Alaska, USA from 2017-06-01 to 2021-04-27 (NCEI Accession 0247208)'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7184,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/4kr2-jc55' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/sentinels-light-trap-public/blob/main/docs/Protocols/2024%20Light%20Trap%20Protocols.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1cyodfkonv4nbh8c_tb9re4ra-8cxjkz7/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1GO3hrEXNGrfRjAYD24fLVe20DZ1T63YT/view?usp=sharing' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7364,12 +7364,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Margot Hessing-Lewis' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alyssa Gehman' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=1jukkkqR46AAO14Q80XMWzwojRotSkuYS returned status_code=404</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/t8hm-ge90' in CKAN not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7499,12 +7499,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/t8hm-ge90' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7544,12 +7544,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7589,12 +7589,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7604,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7634,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7754,12 +7754,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'A. A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -7799,12 +7799,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>bdc6c492-dbb1-4d6e-90b8-d7bddf2c6356</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>a4e3915d-207e-493d-97ff-c1e6ad6f0ce7</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7844,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>e1baeb3c-b764-434c-b0eb-7cb43fe5ef7a</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0209049</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>8bcf556e-26e2-41d4-af2c-2192c0426523</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Underway Surface Seawater and Marine Boundary Layer Observations from the M/V Columbia (Research)' | DataCite='Surface underway measurements partial pressure of carbon dioxide (pCO2) in the water and atmosphere, sea surface salinity, sea surface temperature, oxygen and other parameters during the Alaska Marine Highway System M/V Columbia 135 service route transits along British Columbia coast, southeast Alaska coast, Gulf of Alaska and North Pacific Ocean from 2017-10-26 to 2019-10-04 (NCEI Accession 0209049)'</t>
+          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7949,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://www.hakai.org/blog/life-at-hakai/great-walls-quadra returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Keith Holmes' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>50037e63-bfac-4b7a-8547-56337fe40026</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>35dd16d8-20b1-49d5-8c59-9cdc02475cd0</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>c2b05382-684f-4349-a64b-b20521223574</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8084,12 +8084,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/ytgc-6g46' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/zjc2-b004' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8114,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/zjc2-b004' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/ytgc-6g46' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8309,12 +8309,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>d576481a-4f51-40eb-85e9-fb95933f94cd</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1vzyfwx7jwwlxw8wosydkfgt7vxydwlan/view' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://docs.google.com/document/d/1j4ENgAW_2XtIHzDYbL8u2E5kOK2JkPEBVYdxcuv8NrE/edit?usp=drive_web&amp;ouid=110988987704080303629' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8384,12 +8384,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2168fd41-96d4-4b72-b5ec-0a5c342aad2a</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
         </is>
       </c>
     </row>
@@ -8474,12 +8474,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'H.J. van Meerveld' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'M.J. Waterloo' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208638</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 analyzer located at the Hakai Institute’s Quadra Island Field Station, Hyacinthe Bay, BC, Canada (Research)' | DataCite='High-resolution record of surface seawater carbon dioxide (CO2) content collected from Hakai Institute Quadra Island Field Station in Hyacinthe Bay, British Columbia, Canada from 2014-12-19 to 2025-12-18 (NCEI Accession 0208638)'</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
+          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf returned status_code=timeout</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>08d2c4ef-d157-480d-b3a9-6d0210c8d6ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/n0h9-cq15</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/66x5-a210</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Duplicate DOI shared with another record: 10.21966/rf3y-8j78</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -8849,12 +8849,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>fa913b04-1c29-4449-a78a-466f6b4fb110</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Janusson, Carly</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>a0ada4b0-faea-4dcd-b9bf-d7ff212315fb</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Janusson, Carly</t>
+          <t>Contact missing ORCID: Krkosek, Martin</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Godwin, Sean</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian J. W.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9074,12 +9074,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Krkosek, Martin</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -9104,12 +9104,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Godwin, Sean</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9134,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Menounos, Brian</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9164,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Opie, Rumer</t>
         </is>
       </c>
     </row>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Menounos, Brian</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9254,12 +9254,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9284,12 +9284,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9299,12 +9299,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Wickham, Sara</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Opie, Rumer</t>
+          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Organization missing ROR: University of British Columbia</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
         </is>
       </c>
     </row>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Wickham, Sara</t>
+          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: St. Pierre, Kyra A.</t>
+          <t>Contact missing ORCID: Lertzman, Ken P.</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian P. V.</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -9479,12 +9479,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Kellogg, Colleen T. E.</t>
+          <t>Contact missing ORCID: Barrette, Jessy</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Jackson, Jennifer M.</t>
+          <t>Contact missing ORCID: Savage, Rosie</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Lertzman, Ken P.</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Hunt, Brian</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9584,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Organization missing ROR: University of British Columbia</t>
+          <t>Contact missing ORCID: Weekes, Carrie</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9614,12 +9614,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Barrette, Jessy</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Savage, Rosie</t>
+          <t>Contact missing ORCID: Korver, Maartje</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hunt, Brian</t>
+          <t>Organization missing ROR: Hakai Institute</t>
         </is>
       </c>
     </row>
@@ -9689,12 +9689,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Organization missing ROR: Tula Foundation</t>
         </is>
       </c>
     </row>
@@ -9704,12 +9704,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Weekes, Carrie</t>
+          <t>Contact missing ORCID: Olson, Angeleen</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Organization missing ROR: Simon Fraser University</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Korver, Maartje</t>
+          <t>Contact missing ORCID: Prentice, Carolyn</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Haughton, Emily R.</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Hakai Institute</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Tula Foundation</t>
+          <t>Contact missing ORCID: Brunsting, Ray</t>
         </is>
       </c>
     </row>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olson, Angeleen</t>
+          <t>Contact missing ORCID: Hateley, Shawn</t>
         </is>
       </c>
     </row>
@@ -9839,12 +9839,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9854,12 +9854,12 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Organization missing ROR: Simon Fraser University</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>5143957b-ee18-44d3-8000-a9c8f9a34a0d</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9884,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
+          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Prentice, Carolyn</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily R.</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Giesbrecht, Ian</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9929,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Brunsting, Ray</t>
+          <t>Contact missing ORCID: Haughton, Emily</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hateley, Shawn</t>
+          <t>Contact missing ORCID: Desmarais, Isabelle</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>a9527050-a108-46f7-ac9f-7150b4abede5</t>
+          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Hales, Burke</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10004,12 +10004,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>0ca539a4-217f-43ff-947e-5679dd8d64dd</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
         </is>
       </c>
     </row>
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>5b4d3afa-e0bd-417f-ba08-437cc7e7f864</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Gehman, Alyssa</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Giesbrecht, Ian</t>
+          <t>Contact missing ORCID: Olsen, Angeleen</t>
         </is>
       </c>
     </row>
@@ -10049,12 +10049,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Haughton, Emily</t>
+          <t>Contact missing ORCID: Monteith, Zach</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Desmarais, Isabelle</t>
+          <t>Contact missing ORCID: McInnes, Will</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>6ce6e697-d539-41b1-9771-b5e859a6ff50</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Reshitnyk, Luba</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Olsen, Angeleen</t>
+          <t>Contact missing ORCID: Froese, Tyrel</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>46377bf0-06d5-4612-970d-29cd972e4870</t>
+          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>78b2edef-dab3-47a9-93bb-af63dfcd178d</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hales, Burke</t>
+          <t>Contact missing ORCID: Evans, Wiley</t>
         </is>
       </c>
     </row>
@@ -10184,12 +10184,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2dd906f9-e0fe-4b8c-afe6-c5f2bf7400ae</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: McInnes, Will</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Hessing-Lewis, Margot</t>
+          <t>Contact missing ORCID: Burt, Jenn</t>
         </is>
       </c>
     </row>
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Gehman, Alyssa</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Froese, Tyrel</t>
+          <t>Contact missing ORCID: Tank, Suzanne E.</t>
         </is>
       </c>
     </row>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>967f98cb-131a-421e-bcfd-467cff973b30</t>
+          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Monteith, Zach</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Viner, Nick</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>22951dd4-a9f7-4f2a-b11d-d50e184dc223</t>
+          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Reshitnyk, Luba</t>
+          <t>Contact missing ORCID: Holmes, Keith</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Evans, Wiley</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Floyd, William C.</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>fd691f42-76e9-4e18-80b1-9fb0d6960d95</t>
+          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Burt, Jenn</t>
+          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10334,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
+          <t>Contact missing ORCID: Whalen, Matt</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Tank, Suzanne E.</t>
+          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>
@@ -10364,12 +10364,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
+          <t>Contact missing ORCID: Korver, Maartje C.</t>
         </is>
       </c>
     </row>
@@ -10379,12 +10379,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>e1c64faf-88ac-4d28-8144-fad156971b4e</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Viner, Nick</t>
+          <t>Contact missing ORCID: van Meerveld, H.J.</t>
         </is>
       </c>
     </row>
@@ -10394,132 +10394,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>693c7ca7-a244-4375-9460-ff7c27187af2</t>
+          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Contact missing ORCID: Holmes, Keith</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="n">
-        <v>665</v>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="n">
-        <v>666</v>
-      </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
-        <is>
           <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="n">
-        <v>667</v>
-      </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Whalen, Matt</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="n">
-        <v>668</v>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>fd4f6cd0-c6aa-4061-8caa-0ccade085615</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Gonzalez Arriola, Santiago</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="n">
-        <v>669</v>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Korver, Maartje C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="n">
-        <v>670</v>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: van Meerveld, H.J.</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="n">
-        <v>671</v>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>3a6e9472-1a85-48e5-8ac6-792945e03045</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Floyd, William C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="n">
-        <v>672</v>
-      </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>79433a1f-ec07-4cd5-a31a-8c2c53069085</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>Contact missing ORCID: Hare, Alex</t>
         </is>
       </c>
     </row>

--- a/main/issues_list.xlsx
+++ b/main/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C666"/>
+  <dimension ref="A1:C669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ee09830d-dd5e-41eb-8aee-0fe9cef5fe79</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jenn Burt' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Emily R. Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'GeoBC TRIM Program' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>bfad4541-a06a-489e-bd95-a5e7c65e0dc1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'TRIM BC Base Annotations data' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Shawn Hateley' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>a31d44d5-2ce5-4d03-8d0b-4549023840ff</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
+          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>1bba6c8a-b99c-4fbd-8eae-7c8b771a841d</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier '10.1098/rspb.2020.0108' (HasPart) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4f9103f8-cd13-4bb1-a86b-a3ceb201db97</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier 'http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
+          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7ed2118f-ecaa-41e4-aa81-911ffa47bf34</t>
+          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Gillian Sadlier-Brown' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>b5de5a97-7498-4e5a-8f5d-0850f9e5fc87</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Margot Hessing-Lewis' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/e5c1-c396' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/3s9g-w013' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>f8f299be-a37e-43bf-9416-5ff59e664f65</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>8275a332-8870-4300-8ca8-48b854e7dccf</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>f6ad9487-d689-41a3-b610-352224d7759b</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://npafc.org/wp-content/uploads/Public-Documents/2018/1790Canada.pdf' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>f2f9c9d6-0385-4732-b7d5-acc6bbb2e83a</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Santiago Gonzalez Arriola' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ian J. W. Giesbrecht' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'F. E. Biles' in CKAN record not found in DataCite</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D. V. D'Amore' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://zenodo.org/records/4005400</t>
+          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Differential infestation of juvenile Pacific salmon by parasitic sea lice in British Columbia, Canada' | DataCite='colebrookson/Juv-Pacific-Salmon-Sealice: v1.0'</t>
+          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Martin Krkosek' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brett Johnson' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>8ad491b8-58a3-48ad-a705-18e36fad34b0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Luke Rogers' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Sean Godwin' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.5281/zenodo.8323070' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1139/cjfas-2020-0160' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://hakai-segmentation.readthedocs.io/en/latest/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2709d7b1-22e1-4268-bcda-dc0c79f2878e</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.5281/zenodo.4005399' (IsVersionOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>b1d18883-a622-4f3c-9892-57564271e009</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://obis.org/dataset/80afee46-3e18-4669-ad1b-00f71b0544f5' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.21966/1.521066' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>f15f9c5e-08a6-4e9f-8ff5-a6126447e138</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.48321/d16d6f987c' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>abd11340-660f-48b0-8bf0-9ccb142f513d</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1mt2v_uv78afjp5z_lhi1gu52bqwko4ms/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>876027b6-cf37-4d49-8c3d-22d40b5f5b0b</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Alex Hare' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>4a9b4584-a5ef-4baf-9d4a-bacf8e6a5d1d</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Oceanographic Mooring Time Series, Rivers Inlet, BC, Canada (Research)' | DataCite='Hakai Mooring Water Properties Timeseries Research'</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>074ffcad-2e2f-496c-9378-dec5289d4336</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1darjhrdmvvzesny0d_8arbos95rkufjr/view?usp=drive_link' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Drew Jordison' in DataCite not found in CKAN record</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/g7zf-1v08' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>cb9c0488-666b-4869-9ca4-04d7125fdf8a</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/kace-2d24' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
+          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: version CKAN='1' | DataCite='1.0'</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Jennifer Jackson' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Chris Mackenzie' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: author 'Brian Hunt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Stephanie Waterman' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related identifier '10.1029/2020JC017033' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2909,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
+          <t>a7a3cb32-66ff-4dcb-b05a-2c71511bd115</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0246099</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA' | DataCite='High-resolution record of surface seawater CO2 content from 2016-08 to 2019-05 from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA (NCEI Accession 0246099)'</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: related work '10.21966/pk18-z035' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/erddap/tabledap/hakaiketchikanbolresearch.html' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://10.1029/2025gl115235' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>44754736-c8be-49b1-8806-a0ca4a78255a</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related work '10.21966/36hp-7f40' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://www.onsetcomp.com/products/data-loggers/mx2203/' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/5n09-aq76' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/5n09-aq76' (IsPartOf) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://catalogue.hakai.org/dataset/ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
+          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'M Korver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Maartje C. Korver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Emily Haughton' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'William C. Floyd' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>8c6f32be-1f60-4fcb-bf8b-a63cbac302f7</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Ray Brunsting' in CKAN record not found in DataCite</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
+          <t>75a7ec78-6f48-41f3-92c4-9b734206d6af</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Empty resource name</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related identifier 'https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>d64fd03b-46d4-4662-a123-c11bc42199b6</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>3031aa60-689f-4b94-9dc6-9912cc742431</t>
+          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1yg1ec4-lvj0ut6csylv0p1udmcq-a5xu/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/2aap-hn61' in CKAN not found in DataCite</t>
+          <t>Empty resource name</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1JzY5ELRe1sIbZdq7wBmAOT1t7Y1dNJ2v/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>b47e53cd-74dd-4580-80d0-260860064f4b</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Debora Obrist' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://books.google.ca/books/about/Marine_Phytoplankton.html?id=_lgVAQAAIAAJ&amp;redir_esc=y' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://www.sciencedirect.com/book/9780126930153/identifying-marine-diatoms-and-dinoflagellates' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>6b93216b-4bbe-4204-a2c3-551a667d00fd</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://library-archives.canada.ca/eng/services/services-libraries/theses/Pages/item.aspx?idNumber=30361177' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work 'http://ipt.iobis.org/obiscanada/resource?r=hakai_jsp' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>c68b9ec8-9f26-4fb0-9333-79730f4ea1ca</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.' | DataCite='Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Allison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
+          <t>b276330c-4ee9-476a-979a-cebe52d51db6</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Science' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
+          <t>d1d07d48-c909-41b4-8c0f-13238720749c</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>b307d1bd-61be-4059-b4af-db36555dbd77</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'David J. Levy-Booth' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.' | DataCite='Organic Carbon at Land-Ocean Interface - Calvert Island - 2014-2016'</t>
+          <t>Metadata mismatch: author 'T.J. Heger' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'A. A. Oliver' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'D.V. D’Amore' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Alison A. Oliver' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'P.J. Keeling' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'S.J. Hallam' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'W.W. Mohn' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.21966/1.566666' in CKAN not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4349,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>b3e5b67d-2425-4a4f-80b0-d1076df5492a</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1016/j.rse.2018.06.039' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.1371/journal.pone.0271477' (IsDerivedFrom) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4439,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>151f5813-8d7c-4042-8b7a-a878c814145e</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>4f1e8eac-8390-44d8-93d6-9263fc1dfcf9</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Metadata mismatch: title CKAN='Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)' | DataCite='High performance liquid chromatography phytoplankton pigment timeseries for the northern Salish Sea and central coast, British Columbia'</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: related identifier 'https://ntrs.nasa.gov/citations/20110008482' (IsDocumentedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>dc84cb4c-ba14-4632-a595-eed526bf9db1</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
+          <t>362130df-bc83-48b7-80f9-ad11ad6a91c9</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>384dbb32-4bc8-4bd1-a741-6abbd332a50a</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Airborne Coastal Observatory' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
+          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='1.0.4' | DataCite='1.0.0'</t>
+          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://10.21966/cqrt-sk09' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1crbcqqcmvk3ibyxufqxgj7yv7s5a2-1y/view?usp=sharing' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1ZgcHBPDNHUNRvoaYmpj-IcbDrtPWoviN/view?usp=sharing' (HasMetadata) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4769,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4784,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
+          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
+          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>f1f4ee29-1d0d-49f9-9a5b-64768f24a6ff</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4874,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>DOI is not redirecting to Hakai's catalogue: https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0208810</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/1.566666' (Continues) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: title CKAN='Surface Seawater and Marine Boundary Layer CO2 Observations from the Kwakshua Channel (KC) Buoy on the Central Coast of British Columbia (Research)' | DataCite='Surface seawater and marine boundary layer partial pressure of carbon dioxide (pCO2), temperature and salinity observations made from the Kwakshua Channel (KC) Buoy off the central coast of British Columbia (NCEI Accession 0208810)'</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2a104224-c3eb-4778-adc3-865b36471b1b</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.14288/1.0396439' (IsSourceOf) in DataCite not found in CKAN</t>
+          <t>Metadata mismatch: creator 'Katie Pocock' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
+          <t>3f883dc6-56ac-42f5-a1d4-6de554a9e63d</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Metadata mismatch: author 'Katie Campbell' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>36e9e6ae-a407-456e-8fe2-a3a78b246bf7</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5009,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work '10.1016/j.rse.2021.112317' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5129,12 +5129,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>cd3ca52d-dc83-4501-9e53-7b00c8ab9090</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5204,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>dcde7ad3-f54e-4210-ae4e-33db5aac63fe</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>No publisher</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
+          <t>No publisher</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>f51d96b5-1827-4aab-b1ce-575faff1fd03</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='3.1.0' | DataCite='3.0'</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: author 'Wiley Evans' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Metadata mismatch: author 'Katie Pocock' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>ee30aa86-e786-4a3f-b90f-df09a134621d</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
+          <t>Metadata mismatch: author 'Carrie Weekes' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Metadata mismatch: related work 'https://hakai.maps.arcgis.com/home/webmap/viewer.html?webmap=75ee2603aa5a45068c7e3579796c3aab' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No projects associated</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>21ee0a17-9de0-49d7-9b04-cb9d5f557e9f</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>52048599-9a0c-4d33-861f-26eaedc86bd5</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>No projects associated</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c 